--- a/data/trans_orig/Q45A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q45A_R-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2007</t>
+          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15520</t>
+          <t>15564</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13206</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22682</t>
+          <t>22749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35175</t>
+          <t>34051</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62335</t>
+          <t>61153</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21851</t>
+          <t>21779</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>42860</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63276</t>
+          <t>63705</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95600</t>
+          <t>94976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>188996</t>
+          <t>192254</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>234753</t>
+          <t>233567</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>141907</t>
+          <t>142840</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>175223</t>
+          <t>176980</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>343269</t>
+          <t>342566</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>400481</t>
+          <t>396221</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>50,77%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>99153</t>
+          <t>98236</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>136730</t>
+          <t>135585</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49788</t>
+          <t>49475</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79520</t>
+          <t>77826</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>158636</t>
+          <t>157214</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>206436</t>
+          <t>206717</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70925</t>
+          <t>71557</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>105911</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35833</t>
+          <t>36181</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62160</t>
+          <t>61722</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114226</t>
+          <t>117085</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158760</t>
+          <t>159443</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9747</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13963</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19185</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19549</t>
+          <t>19864</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39821</t>
+          <t>39841</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34846</t>
+          <t>34955</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59500</t>
+          <t>60144</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59864</t>
+          <t>59575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91143</t>
+          <t>92292</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>173121</t>
+          <t>172924</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>212696</t>
+          <t>212833</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>179939</t>
+          <t>179268</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>218294</t>
+          <t>216786</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>366655</t>
+          <t>365643</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>418611</t>
+          <t>419831</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,83%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69629</t>
+          <t>68741</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105251</t>
+          <t>101890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49168</t>
+          <t>49290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78714</t>
+          <t>77307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126019</t>
+          <t>126763</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169637</t>
+          <t>170770</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42451</t>
+          <t>42878</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71658</t>
+          <t>72674</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44174</t>
+          <t>45011</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72543</t>
+          <t>73856</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93194</t>
+          <t>94323</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>136976</t>
+          <t>135393</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>8847</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26837</t>
+          <t>26678</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>8858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25155</t>
+          <t>25374</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28207</t>
+          <t>27983</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54236</t>
+          <t>52991</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15103</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35502</t>
+          <t>36299</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62315</t>
+          <t>61339</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>220847</t>
+          <t>220907</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>269511</t>
+          <t>266730</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69008</t>
+          <t>70129</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>95655</t>
+          <t>95730</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>299733</t>
+          <t>300146</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>353504</t>
+          <t>354247</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,88%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>121847</t>
+          <t>120587</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>162979</t>
+          <t>163958</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25970</t>
+          <t>26658</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47234</t>
+          <t>47108</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>155256</t>
+          <t>156524</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>202461</t>
+          <t>201354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83456</t>
+          <t>85039</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>121248</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30778</t>
+          <t>29796</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52519</t>
+          <t>53340</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>123058</t>
+          <t>120513</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165161</t>
+          <t>165548</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19936</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42697</t>
+          <t>42740</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7316</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>22644</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31551</t>
+          <t>30802</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59228</t>
+          <t>57721</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107950</t>
+          <t>107751</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>151318</t>
+          <t>150685</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>45486</t>
+          <t>46995</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>76625</t>
+          <t>75644</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>163406</t>
+          <t>163925</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>217728</t>
+          <t>215774</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>526281</t>
+          <t>525784</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>596830</t>
+          <t>595782</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>293607</t>
+          <t>293941</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>346287</t>
+          <t>346930</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>836226</t>
+          <t>834546</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>924764</t>
+          <t>920712</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>242453</t>
+          <t>244640</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>302155</t>
+          <t>299615</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>163889</t>
+          <t>163336</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>211587</t>
+          <t>211029</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>423104</t>
+          <t>424972</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>496588</t>
+          <t>496920</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>218673</t>
+          <t>220160</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>278062</t>
+          <t>278341</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>112544</t>
+          <t>113750</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>154761</t>
+          <t>156269</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>347593</t>
+          <t>348511</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>416909</t>
+          <t>419820</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24971</t>
+          <t>24367</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>13304</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32003</t>
+          <t>31460</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>44753</t>
+          <t>44815</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>72933</t>
+          <t>74912</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22828</t>
+          <t>22261</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45657</t>
+          <t>44486</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>74537</t>
+          <t>72667</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>109331</t>
+          <t>109929</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>145244</t>
+          <t>146153</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>182642</t>
+          <t>183279</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>234014</t>
+          <t>233518</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>282238</t>
+          <t>282422</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>393549</t>
+          <t>389706</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>453248</t>
+          <t>451290</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>34131</t>
+          <t>34006</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>58644</t>
+          <t>58641</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>120329</t>
+          <t>119490</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>162253</t>
+          <t>162841</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>161195</t>
+          <t>160385</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>210584</t>
+          <t>208852</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>61530</t>
+          <t>61477</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>92803</t>
+          <t>91525</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>105942</t>
+          <t>104954</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>145137</t>
+          <t>145300</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>177218</t>
+          <t>175579</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>228605</t>
+          <t>226271</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>8630</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>23999</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>12578</t>
+          <t>12044</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>29964</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>30891</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>54825</t>
+          <t>52870</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>75089</t>
+          <t>74341</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>111387</t>
+          <t>113518</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>113266</t>
+          <t>112777</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>154132</t>
+          <t>156951</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>170823</t>
+          <t>169699</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>204756</t>
+          <t>203058</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>576623</t>
+          <t>577631</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>648960</t>
+          <t>651006</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>762041</t>
+          <t>761903</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>837888</t>
+          <t>837641</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>29759</t>
+          <t>29101</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>53423</t>
+          <t>52252</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>206872</t>
+          <t>207172</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>263078</t>
+          <t>263088</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>244522</t>
+          <t>247219</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>304906</t>
+          <t>305732</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>17277</t>
+          <t>17293</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>37007</t>
+          <t>36738</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>264264</t>
+          <t>266406</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>324946</t>
+          <t>326280</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>291164</t>
+          <t>289751</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>356114</t>
+          <t>352066</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>52590</t>
+          <t>51378</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>87590</t>
+          <t>86996</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>42606</t>
+          <t>43007</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>71320</t>
+          <t>74037</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>103613</t>
+          <t>101711</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>149936</t>
+          <t>148738</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>306291</t>
+          <t>310196</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>378681</t>
+          <t>376318</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>239261</t>
+          <t>236557</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>303093</t>
+          <t>298778</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>563322</t>
+          <t>566140</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>660072</t>
+          <t>656880</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1505027</t>
+          <t>1505112</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1619688</t>
+          <t>1617388</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1571941</t>
+          <t>1571470</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1689265</t>
+          <t>1687812</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3115034</t>
+          <t>3110697</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3273216</t>
+          <t>3273591</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,25%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>649141</t>
+          <t>655115</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>747877</t>
+          <t>749227</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>676518</t>
+          <t>678650</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>768598</t>
+          <t>771345</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1358786</t>
+          <t>1357527</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1493646</t>
+          <t>1490365</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>555627</t>
+          <t>551812</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>645498</t>
+          <t>644041</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>653845</t>
+          <t>657149</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>748483</t>
+          <t>751284</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1230463</t>
+          <t>1227667</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1359300</t>
+          <t>1355076</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2012</t>
+          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2012 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>8825</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14278</t>
+          <t>14161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31714</t>
+          <t>31816</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57817</t>
+          <t>57782</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19848</t>
+          <t>19625</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41448</t>
+          <t>40088</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57022</t>
+          <t>57292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90420</t>
+          <t>95251</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>165242</t>
+          <t>165257</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>209118</t>
+          <t>209411</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>103089</t>
+          <t>103857</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139608</t>
+          <t>141373</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>281596</t>
+          <t>279918</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>337722</t>
+          <t>337042</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79037</t>
+          <t>79600</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116136</t>
+          <t>116825</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56750</t>
+          <t>55998</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87577</t>
+          <t>87029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143487</t>
+          <t>144672</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>193101</t>
+          <t>191941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88018</t>
+          <t>89396</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>128119</t>
+          <t>127978</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72191</t>
+          <t>72319</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106735</t>
+          <t>105967</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170634</t>
+          <t>170650</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>223016</t>
+          <t>223797</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17321</t>
+          <t>18083</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9359</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26411</t>
+          <t>24300</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29131</t>
+          <t>28017</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54050</t>
+          <t>53167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22866</t>
+          <t>23457</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45190</t>
+          <t>46436</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56895</t>
+          <t>56424</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93398</t>
+          <t>90984</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>163806</t>
+          <t>164379</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>206884</t>
+          <t>206336</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>125191</t>
+          <t>125121</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>163384</t>
+          <t>162806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>302130</t>
+          <t>304634</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>359841</t>
+          <t>361221</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64604</t>
+          <t>67268</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104276</t>
+          <t>103433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53482</t>
+          <t>54429</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84101</t>
+          <t>85232</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128473</t>
+          <t>130032</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176318</t>
+          <t>176641</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85668</t>
+          <t>86315</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>122808</t>
+          <t>123782</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66189</t>
+          <t>67110</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>98051</t>
+          <t>101851</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>161677</t>
+          <t>162696</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>212055</t>
+          <t>213388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21857</t>
+          <t>22299</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24736</t>
+          <t>23541</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51279</t>
+          <t>50708</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81280</t>
+          <t>81397</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10770</t>
+          <t>10944</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27247</t>
+          <t>29569</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66266</t>
+          <t>65874</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101710</t>
+          <t>101301</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>198365</t>
+          <t>198553</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>248593</t>
+          <t>246732</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81224</t>
+          <t>81603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>112520</t>
+          <t>112310</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>290861</t>
+          <t>290996</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>347864</t>
+          <t>346765</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>123842</t>
+          <t>124237</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>167046</t>
+          <t>167820</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49999</t>
+          <t>49421</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77525</t>
+          <t>78650</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>181073</t>
+          <t>183522</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>234040</t>
+          <t>235267</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157997</t>
+          <t>160390</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206424</t>
+          <t>206457</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65294</t>
+          <t>63512</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95732</t>
+          <t>95022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>235741</t>
+          <t>236433</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>290615</t>
+          <t>292701</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>20787</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44261</t>
+          <t>43623</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21031</t>
+          <t>20342</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30333</t>
+          <t>30526</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57187</t>
+          <t>56753</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>84614</t>
+          <t>84048</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>126025</t>
+          <t>125814</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>64007</t>
+          <t>64952</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>98238</t>
+          <t>99534</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>156603</t>
+          <t>159102</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>212128</t>
+          <t>212156</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>347368</t>
+          <t>345953</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>411910</t>
+          <t>410177</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>255644</t>
+          <t>256117</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>310224</t>
+          <t>311313</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>622094</t>
+          <t>617717</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>705344</t>
+          <t>704136</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>232706</t>
+          <t>230821</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>291242</t>
+          <t>290821</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>133156</t>
+          <t>131496</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>177571</t>
+          <t>176702</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>379969</t>
+          <t>381645</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>452922</t>
+          <t>458114</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>351335</t>
+          <t>351091</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>417595</t>
+          <t>416943</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>210624</t>
+          <t>210830</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>263669</t>
+          <t>262948</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>575700</t>
+          <t>576193</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>662028</t>
+          <t>665864</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5354</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20615</t>
+          <t>19640</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9011</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25890</t>
+          <t>26796</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>46606</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>77703</t>
+          <t>78380</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>32099</t>
+          <t>34573</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>61563</t>
+          <t>61380</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>88439</t>
+          <t>89794</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>130388</t>
+          <t>131854</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>156045</t>
+          <t>153540</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>199086</t>
+          <t>198595</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>181412</t>
+          <t>179527</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>230855</t>
+          <t>234035</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>342576</t>
+          <t>350846</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>411679</t>
+          <t>418205</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>83406</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>118999</t>
+          <t>117273</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>153399</t>
+          <t>155536</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>203411</t>
+          <t>204726</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>249998</t>
+          <t>247351</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>307073</t>
+          <t>306015</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>146476</t>
+          <t>146809</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>191915</t>
+          <t>192016</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>292494</t>
+          <t>290000</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>350194</t>
+          <t>347025</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,47 +8970,47 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
+          <t>38,14%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>45,64%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>488967</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>451446</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>522805</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
           <t>38,47%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>46,06%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>488967</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>458550</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>531032</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>38,47%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,13%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5097</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18005</t>
+          <t>18821</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7720</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>22730</t>
+          <t>23084</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>33593</t>
+          <t>33270</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>57359</t>
+          <t>56184</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>82165</t>
+          <t>81608</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>123031</t>
+          <t>123863</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>124312</t>
+          <t>123487</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>170188</t>
+          <t>170470</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>122947</t>
+          <t>123308</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>155881</t>
+          <t>155417</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>330993</t>
+          <t>333350</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>391535</t>
+          <t>394609</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>465977</t>
+          <t>465136</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>539336</t>
+          <t>534449</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>23856</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>46837</t>
+          <t>48439</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>238214</t>
+          <t>238608</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>293937</t>
+          <t>295781</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>275163</t>
+          <t>273659</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>338210</t>
+          <t>335492</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>34592</t>
+          <t>34310</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>59204</t>
+          <t>59351</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>332692</t>
+          <t>336518</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>398880</t>
+          <t>399279</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>374159</t>
+          <t>377392</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>444686</t>
+          <t>447628</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>44346</t>
+          <t>43909</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>78516</t>
+          <t>76482</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>36939</t>
+          <t>37503</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>65204</t>
+          <t>65318</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>89041</t>
+          <t>88792</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>133314</t>
+          <t>131264</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>319203</t>
+          <t>321809</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>391187</t>
+          <t>397378</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>275270</t>
+          <t>272793</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>347966</t>
+          <t>342565</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>616316</t>
+          <t>620056</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>713860</t>
+          <t>723923</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1229832</t>
+          <t>1223221</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1349100</t>
+          <t>1349642</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1157325</t>
+          <t>1155000</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1271970</t>
+          <t>1274968</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2426944</t>
+          <t>2413872</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2575163</t>
+          <t>2577926</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>673198</t>
+          <t>672598</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>775145</t>
+          <t>773854</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>746803</t>
+          <t>746296</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>848656</t>
+          <t>846700</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1453818</t>
+          <t>1445263</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1593516</t>
+          <t>1589273</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>937176</t>
+          <t>937937</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1051383</t>
+          <t>1053711</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1114918</t>
+          <t>1115029</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1227820</t>
+          <t>1229525</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2087333</t>
+          <t>2088464</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2231960</t>
+          <t>2247247</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2016</t>
+          <t>Población según la frecuencia de haber estado expuesto al sol entre las 12 de la mañana y las 5 de la tarde el pasado verano en 2016 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12193</t>
+          <t>12400</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10804</t>
+          <t>11434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45513</t>
+          <t>44082</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74477</t>
+          <t>73827</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30116</t>
+          <t>29772</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54284</t>
+          <t>52902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82363</t>
+          <t>81930</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120462</t>
+          <t>119486</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>140926</t>
+          <t>140268</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>181586</t>
+          <t>183164</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>121067</t>
+          <t>120262</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>156711</t>
+          <t>158393</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>274541</t>
+          <t>273290</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>330471</t>
+          <t>328297</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>126986</t>
+          <t>125590</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>166178</t>
+          <t>165138</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88444</t>
+          <t>88529</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122389</t>
+          <t>123142</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>220515</t>
+          <t>222138</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>275253</t>
+          <t>275011</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46617</t>
+          <t>45454</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74643</t>
+          <t>76169</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44060</t>
+          <t>44071</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73035</t>
+          <t>72395</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98345</t>
+          <t>96451</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>138987</t>
+          <t>137409</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>10611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11971</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18007</t>
+          <t>18210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37016</t>
+          <t>39329</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66791</t>
+          <t>67621</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41947</t>
+          <t>41205</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69186</t>
+          <t>68286</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89614</t>
+          <t>87520</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>129771</t>
+          <t>126944</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>110880</t>
+          <t>109787</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>148230</t>
+          <t>146262</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>122431</t>
+          <t>123357</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>161638</t>
+          <t>160715</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>245803</t>
+          <t>242422</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>296132</t>
+          <t>298251</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,96%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115451</t>
+          <t>114439</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>152534</t>
+          <t>150760</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103154</t>
+          <t>102403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141037</t>
+          <t>141032</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>227681</t>
+          <t>226252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>281709</t>
+          <t>280099</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45606</t>
+          <t>44491</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74917</t>
+          <t>73604</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36459</t>
+          <t>35752</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64499</t>
+          <t>63121</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88050</t>
+          <t>87882</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128733</t>
+          <t>128166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14147</t>
+          <t>13234</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60855</t>
+          <t>60015</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93471</t>
+          <t>91969</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23250</t>
+          <t>22572</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73124</t>
+          <t>74635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>109871</t>
+          <t>109939</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>139791</t>
+          <t>142492</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>182206</t>
+          <t>185712</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37202</t>
+          <t>36853</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60817</t>
+          <t>61006</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>189019</t>
+          <t>186452</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>237641</t>
+          <t>234410</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>152897</t>
+          <t>154358</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>194473</t>
+          <t>197164</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41686</t>
+          <t>41878</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65254</t>
+          <t>66853</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>203134</t>
+          <t>203795</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>253083</t>
+          <t>252406</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,75%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86174</t>
+          <t>85903</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123523</t>
+          <t>122895</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38324</t>
+          <t>37633</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63494</t>
+          <t>61810</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>130475</t>
+          <t>132623</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>177250</t>
+          <t>177893</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>22006</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19039</t>
+          <t>18354</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15048</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34925</t>
+          <t>34645</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>125591</t>
+          <t>127808</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>173713</t>
+          <t>174777</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>89131</t>
+          <t>87562</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>125359</t>
+          <t>125059</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>225663</t>
+          <t>227745</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>285360</t>
+          <t>286674</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>388869</t>
+          <t>390618</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>458262</t>
+          <t>456079</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>273504</t>
+          <t>272655</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>325574</t>
+          <t>329303</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>682310</t>
+          <t>684326</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>765679</t>
+          <t>767777</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>302930</t>
+          <t>298972</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>362189</t>
+          <t>361380</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>224886</t>
+          <t>224219</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>279260</t>
+          <t>276593</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>541400</t>
+          <t>542101</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>620374</t>
+          <t>621181</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>205632</t>
+          <t>206371</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>259895</t>
+          <t>261455</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,82 +13261,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>17,98%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>22,78%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>157043</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>133152</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>181903</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>19,05%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>16,15%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>22,07%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>388636</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>353435</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>424500</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>19,71%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>17,92%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>22,65%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>157043</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>131868</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>178804</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>19,05%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>16,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>388636</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>353939</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>423976</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>19,71%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>17,95%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9224</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26279</t>
+          <t>25654</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>60352</t>
+          <t>61403</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>95761</t>
+          <t>95588</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>36010</t>
+          <t>35545</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>61714</t>
+          <t>62071</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>103472</t>
+          <t>104298</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>146997</t>
+          <t>150190</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>180810</t>
+          <t>179861</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>230229</t>
+          <t>226778</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>193320</t>
+          <t>192798</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>241596</t>
+          <t>243386</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>386564</t>
+          <t>386197</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>454584</t>
+          <t>454221</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,42%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>168297</t>
+          <t>167504</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>213987</t>
+          <t>213799</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>247246</t>
+          <t>248022</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>298584</t>
+          <t>300963</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>432185</t>
+          <t>429623</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>501350</t>
+          <t>501077</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>121655</t>
+          <t>125386</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>163799</t>
+          <t>166113</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>166459</t>
+          <t>164425</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>214225</t>
+          <t>215556</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>301864</t>
+          <t>303099</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>368585</t>
+          <t>366019</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25072</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>25231</t>
+          <t>26096</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>50557</t>
+          <t>50652</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>79072</t>
+          <t>79691</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>104580</t>
+          <t>104943</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>146606</t>
+          <t>148696</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>165973</t>
+          <t>166079</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>217539</t>
+          <t>218322</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>107212</t>
+          <t>108724</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>142146</t>
+          <t>143867</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>285448</t>
+          <t>288542</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>347118</t>
+          <t>349254</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>410017</t>
+          <t>408415</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>480620</t>
+          <t>479504</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>50127</t>
+          <t>50073</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>78744</t>
+          <t>78696</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>272913</t>
+          <t>271971</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>334420</t>
+          <t>330829</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>334730</t>
+          <t>330283</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>398864</t>
+          <t>399540</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>21419</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>44352</t>
+          <t>44656</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>291693</t>
+          <t>290161</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>356991</t>
+          <t>353675</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>317525</t>
+          <t>316895</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>387508</t>
+          <t>385944</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>23469</t>
+          <t>24080</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>47151</t>
+          <t>50780</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>32711</t>
+          <t>33491</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>62016</t>
+          <t>61465</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>63953</t>
+          <t>62976</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>101819</t>
+          <t>101038</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>436155</t>
+          <t>437139</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>519944</t>
+          <t>520479</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>354098</t>
+          <t>354048</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>427486</t>
+          <t>427399</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>811342</t>
+          <t>809176</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>921790</t>
+          <t>923988</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1142582</t>
+          <t>1144301</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1260622</t>
+          <t>1260411</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1107250</t>
+          <t>1110963</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1221171</t>
+          <t>1221508</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2288216</t>
+          <t>2294321</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2444554</t>
+          <t>2448534</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>985822</t>
+          <t>983738</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1093917</t>
+          <t>1090439</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1053339</t>
+          <t>1045880</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1158779</t>
+          <t>1159896</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2062855</t>
+          <t>2066688</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2220080</t>
+          <t>2227465</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>578117</t>
+          <t>581875</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>678524</t>
+          <t>674744</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>773053</t>
+          <t>772916</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>878612</t>
+          <t>875285</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1380403</t>
+          <t>1381541</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1522835</t>
+          <t>1523216</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q45A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q45A_R-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>12700</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22749</t>
+          <t>24458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34051</t>
+          <t>34973</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61153</t>
+          <t>61833</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21779</t>
+          <t>21943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42860</t>
+          <t>42643</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63705</t>
+          <t>63359</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94976</t>
+          <t>97443</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>192254</t>
+          <t>190627</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>233567</t>
+          <t>234784</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>142840</t>
+          <t>142358</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>176980</t>
+          <t>176848</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>342566</t>
+          <t>343781</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>396221</t>
+          <t>399139</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,14%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98236</t>
+          <t>99231</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>135585</t>
+          <t>136841</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49475</t>
+          <t>48307</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77826</t>
+          <t>77174</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>157214</t>
+          <t>156655</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>206717</t>
+          <t>204973</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71557</t>
+          <t>69932</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105911</t>
+          <t>106755</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36181</t>
+          <t>35140</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61722</t>
+          <t>61025</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>117085</t>
+          <t>114756</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>159443</t>
+          <t>158069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19576</t>
+          <t>19485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19864</t>
+          <t>19312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39841</t>
+          <t>38998</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34955</t>
+          <t>33919</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60144</t>
+          <t>59077</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59575</t>
+          <t>59806</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>92292</t>
+          <t>93505</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>172924</t>
+          <t>172578</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>212833</t>
+          <t>212611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>179268</t>
+          <t>180354</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>216786</t>
+          <t>218990</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>365643</t>
+          <t>364726</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>419831</t>
+          <t>418805</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68741</t>
+          <t>70221</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101890</t>
+          <t>103928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49290</t>
+          <t>48952</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77307</t>
+          <t>78146</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126763</t>
+          <t>126900</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170770</t>
+          <t>171263</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42878</t>
+          <t>43323</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72674</t>
+          <t>73763</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45011</t>
+          <t>42824</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73856</t>
+          <t>73602</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94323</t>
+          <t>95714</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135393</t>
+          <t>135267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>8079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26678</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>9156</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25374</t>
+          <t>25093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27983</t>
+          <t>28247</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52991</t>
+          <t>52924</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>15281</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36299</t>
+          <t>35234</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61339</t>
+          <t>60528</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>220907</t>
+          <t>220681</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>266730</t>
+          <t>268127</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70129</t>
+          <t>69861</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>95730</t>
+          <t>95784</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>300146</t>
+          <t>299035</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>354247</t>
+          <t>353213</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,74%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120587</t>
+          <t>121959</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>163958</t>
+          <t>161878</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26658</t>
+          <t>26744</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47108</t>
+          <t>47365</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>156524</t>
+          <t>155785</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>201354</t>
+          <t>199330</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85039</t>
+          <t>83699</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>121822</t>
+          <t>121929</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29796</t>
+          <t>29501</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53340</t>
+          <t>51878</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>120513</t>
+          <t>121563</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165548</t>
+          <t>166590</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20145</t>
+          <t>19151</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42740</t>
+          <t>40660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22644</t>
+          <t>22906</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30802</t>
+          <t>30689</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57721</t>
+          <t>57615</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107751</t>
+          <t>107095</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>150685</t>
+          <t>150427</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>46995</t>
+          <t>45820</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>75644</t>
+          <t>76019</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>163925</t>
+          <t>165360</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>215774</t>
+          <t>216443</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>525784</t>
+          <t>524932</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>595782</t>
+          <t>594717</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>293941</t>
+          <t>294774</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>346930</t>
+          <t>349035</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>834546</t>
+          <t>838436</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>920712</t>
+          <t>924625</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,37%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>244640</t>
+          <t>241817</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>299615</t>
+          <t>301060</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>163336</t>
+          <t>163327</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>211029</t>
+          <t>210811</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>424972</t>
+          <t>420012</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>496920</t>
+          <t>496366</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>220160</t>
+          <t>220257</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>278341</t>
+          <t>273305</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>113750</t>
+          <t>114303</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>156269</t>
+          <t>154303</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>348511</t>
+          <t>348142</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>419820</t>
+          <t>422919</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14300</t>
+          <t>13602</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24367</t>
+          <t>24848</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13304</t>
+          <t>13222</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31460</t>
+          <t>33011</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>44815</t>
+          <t>43114</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>74912</t>
+          <t>72417</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22261</t>
+          <t>21919</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44486</t>
+          <t>43448</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>72667</t>
+          <t>73591</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>109929</t>
+          <t>112036</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>146153</t>
+          <t>143224</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>183279</t>
+          <t>182544</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>233518</t>
+          <t>234581</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>282422</t>
+          <t>281710</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>389706</t>
+          <t>390276</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>451290</t>
+          <t>451554</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>33865</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>58641</t>
+          <t>57824</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>119490</t>
+          <t>120103</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>162841</t>
+          <t>163525</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>160385</t>
+          <t>162147</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>208852</t>
+          <t>209695</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>61477</t>
+          <t>61288</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>91525</t>
+          <t>91776</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>104954</t>
+          <t>105964</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>145300</t>
+          <t>145132</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>175579</t>
+          <t>177619</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>226271</t>
+          <t>230037</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11931</t>
+          <t>11643</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>23446</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>12288</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>29964</t>
+          <t>29797</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>30766</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>52870</t>
+          <t>53939</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>74341</t>
+          <t>75472</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>113518</t>
+          <t>109899</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>112777</t>
+          <t>112386</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>156951</t>
+          <t>156375</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>169699</t>
+          <t>167849</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>203058</t>
+          <t>202141</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>577631</t>
+          <t>576341</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>651006</t>
+          <t>648309</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>761903</t>
+          <t>761970</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>837641</t>
+          <t>841218</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,38%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>29101</t>
+          <t>29505</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>52252</t>
+          <t>52837</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>207172</t>
+          <t>205586</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>263088</t>
+          <t>263586</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>247219</t>
+          <t>246240</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>305732</t>
+          <t>308666</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>17293</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>36738</t>
+          <t>37046</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>266406</t>
+          <t>267600</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>326280</t>
+          <t>327001</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>289751</t>
+          <t>290581</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>352066</t>
+          <t>352675</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>51378</t>
+          <t>53307</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>86996</t>
+          <t>85532</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>43007</t>
+          <t>43268</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>74037</t>
+          <t>72601</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>101711</t>
+          <t>103474</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>148738</t>
+          <t>147691</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>310196</t>
+          <t>305016</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>376318</t>
+          <t>378601</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>236557</t>
+          <t>239877</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>298778</t>
+          <t>303068</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>566140</t>
+          <t>566875</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>656880</t>
+          <t>661081</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1505112</t>
+          <t>1500825</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1617388</t>
+          <t>1621506</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1571470</t>
+          <t>1576052</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1687812</t>
+          <t>1691471</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3110697</t>
+          <t>3112073</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3273591</t>
+          <t>3274924</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,27%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>655115</t>
+          <t>653001</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>749227</t>
+          <t>749370</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>678650</t>
+          <t>672078</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>771345</t>
+          <t>769773</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1357527</t>
+          <t>1362272</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1490365</t>
+          <t>1489534</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>551812</t>
+          <t>552845</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>644041</t>
+          <t>639596</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>657149</t>
+          <t>651256</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>751284</t>
+          <t>745604</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1227667</t>
+          <t>1230900</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1355076</t>
+          <t>1357265</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>12196</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>989</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>8696</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>14697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31816</t>
+          <t>30934</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57782</t>
+          <t>57268</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19625</t>
+          <t>19936</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40088</t>
+          <t>42075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57292</t>
+          <t>57899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95251</t>
+          <t>93100</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>165257</t>
+          <t>166267</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>209411</t>
+          <t>209690</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>103857</t>
+          <t>105619</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>141373</t>
+          <t>141835</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>279918</t>
+          <t>279598</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>337042</t>
+          <t>334957</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79600</t>
+          <t>78836</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116825</t>
+          <t>115356</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55998</t>
+          <t>56610</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87029</t>
+          <t>86684</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144672</t>
+          <t>143228</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>191941</t>
+          <t>193261</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89396</t>
+          <t>88837</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>127978</t>
+          <t>128209</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72319</t>
+          <t>70927</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105967</t>
+          <t>105816</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170650</t>
+          <t>168313</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>223797</t>
+          <t>221536</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12050</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18083</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24300</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28017</t>
+          <t>28803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53167</t>
+          <t>53996</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23457</t>
+          <t>21382</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46436</t>
+          <t>45976</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56424</t>
+          <t>57892</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90984</t>
+          <t>93154</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>164379</t>
+          <t>164836</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>206336</t>
+          <t>207329</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>125121</t>
+          <t>125370</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>162806</t>
+          <t>162932</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>304634</t>
+          <t>303116</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>361221</t>
+          <t>361085</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,71%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67268</t>
+          <t>65926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103433</t>
+          <t>102641</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54429</t>
+          <t>54126</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85232</t>
+          <t>84664</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>130032</t>
+          <t>128655</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176641</t>
+          <t>176060</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86315</t>
+          <t>86362</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123782</t>
+          <t>127214</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67110</t>
+          <t>65488</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101851</t>
+          <t>99150</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>162696</t>
+          <t>161128</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>213388</t>
+          <t>213309</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22299</t>
+          <t>21775</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>8652</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23541</t>
+          <t>24592</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50708</t>
+          <t>50444</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81397</t>
+          <t>81599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10944</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29569</t>
+          <t>26907</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65874</t>
+          <t>66983</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101301</t>
+          <t>103188</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>198553</t>
+          <t>198477</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>246732</t>
+          <t>245891</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81603</t>
+          <t>82111</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>112310</t>
+          <t>113718</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>290996</t>
+          <t>291901</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>346765</t>
+          <t>351885</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,69%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>124237</t>
+          <t>123335</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>167820</t>
+          <t>168512</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49421</t>
+          <t>49296</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78650</t>
+          <t>78437</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>183522</t>
+          <t>182957</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>235267</t>
+          <t>235312</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160390</t>
+          <t>159946</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206457</t>
+          <t>207948</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63512</t>
+          <t>65692</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95022</t>
+          <t>96463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>236433</t>
+          <t>235204</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>292701</t>
+          <t>290992</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20787</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43623</t>
+          <t>44691</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>20861</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30526</t>
+          <t>30773</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56753</t>
+          <t>58712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>84048</t>
+          <t>84235</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>125814</t>
+          <t>125808</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>64952</t>
+          <t>64448</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>99534</t>
+          <t>99055</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>159102</t>
+          <t>158626</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>212156</t>
+          <t>210468</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>345953</t>
+          <t>348338</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>410177</t>
+          <t>414529</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>256117</t>
+          <t>254405</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>311313</t>
+          <t>311740</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>617717</t>
+          <t>619532</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>704136</t>
+          <t>704611</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>230821</t>
+          <t>231576</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>290821</t>
+          <t>290936</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>131496</t>
+          <t>133093</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>176702</t>
+          <t>179763</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>381645</t>
+          <t>378245</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>458114</t>
+          <t>452799</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>351091</t>
+          <t>351285</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>416943</t>
+          <t>415339</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>210830</t>
+          <t>210171</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>262948</t>
+          <t>263121</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>576193</t>
+          <t>578586</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>665864</t>
+          <t>662153</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19640</t>
+          <t>20085</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26796</t>
+          <t>25606</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>46606</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78380</t>
+          <t>78539</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34573</t>
+          <t>34498</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>61380</t>
+          <t>63556</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>89794</t>
+          <t>87643</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>131854</t>
+          <t>130462</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>153540</t>
+          <t>152808</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>198595</t>
+          <t>196562</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>179527</t>
+          <t>180525</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>234035</t>
+          <t>231839</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>350846</t>
+          <t>350586</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>418205</t>
+          <t>413182</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>82855</t>
+          <t>83924</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>117273</t>
+          <t>119588</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>155536</t>
+          <t>152593</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>204726</t>
+          <t>201480</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>247351</t>
+          <t>245383</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>306015</t>
+          <t>307610</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>146809</t>
+          <t>147489</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>192016</t>
+          <t>189595</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>290000</t>
+          <t>293263</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>347025</t>
+          <t>351258</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>451446</t>
+          <t>453672</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>522805</t>
+          <t>526223</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18821</t>
+          <t>18871</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>23084</t>
+          <t>22182</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>33270</t>
+          <t>32708</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>56184</t>
+          <t>56503</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>81608</t>
+          <t>82172</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>123863</t>
+          <t>121539</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>123487</t>
+          <t>122487</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>170470</t>
+          <t>170569</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>123308</t>
+          <t>122250</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>155417</t>
+          <t>155278</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>333350</t>
+          <t>331452</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>394609</t>
+          <t>392301</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>465136</t>
+          <t>467388</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>534449</t>
+          <t>541173</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>25200</t>
+          <t>25787</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>48439</t>
+          <t>47432</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>238608</t>
+          <t>240117</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>295781</t>
+          <t>296755</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>273659</t>
+          <t>273347</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>335492</t>
+          <t>334888</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>34310</t>
+          <t>34014</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>59351</t>
+          <t>58624</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>336518</t>
+          <t>332904</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>399279</t>
+          <t>397248</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>377392</t>
+          <t>380808</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>447628</t>
+          <t>447328</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>43909</t>
+          <t>44018</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>76482</t>
+          <t>76447</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>37503</t>
+          <t>37623</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>65318</t>
+          <t>66203</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>88792</t>
+          <t>88542</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>131264</t>
+          <t>132819</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>321809</t>
+          <t>318213</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>397378</t>
+          <t>389620</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>272793</t>
+          <t>275167</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>342565</t>
+          <t>343532</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>620056</t>
+          <t>617968</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>723923</t>
+          <t>717932</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1223221</t>
+          <t>1228252</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1349642</t>
+          <t>1349589</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1155000</t>
+          <t>1150044</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1274968</t>
+          <t>1269550</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2413872</t>
+          <t>2414292</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2577926</t>
+          <t>2579804</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>672598</t>
+          <t>672555</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>773854</t>
+          <t>770480</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>746296</t>
+          <t>748175</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>846700</t>
+          <t>848149</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1445263</t>
+          <t>1452033</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1589273</t>
+          <t>1593213</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>937937</t>
+          <t>937443</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1053711</t>
+          <t>1046802</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1115029</t>
+          <t>1119350</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1229525</t>
+          <t>1235715</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2088464</t>
+          <t>2084057</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2247247</t>
+          <t>2246704</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>12683</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11434</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18346</t>
+          <t>19389</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44082</t>
+          <t>43899</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73827</t>
+          <t>73626</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29772</t>
+          <t>30115</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52902</t>
+          <t>53963</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81930</t>
+          <t>81387</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119486</t>
+          <t>120366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>140268</t>
+          <t>141753</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>183164</t>
+          <t>183537</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>120262</t>
+          <t>121128</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158393</t>
+          <t>158924</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>273290</t>
+          <t>275721</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>328297</t>
+          <t>330136</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,54%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125590</t>
+          <t>125107</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>165138</t>
+          <t>165116</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88529</t>
+          <t>88501</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123142</t>
+          <t>122328</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>222138</t>
+          <t>219833</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>275011</t>
+          <t>275079</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45454</t>
+          <t>45732</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76169</t>
+          <t>75186</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44071</t>
+          <t>43633</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72395</t>
+          <t>73029</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96451</t>
+          <t>98351</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>137409</t>
+          <t>139022</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10611</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18210</t>
+          <t>17187</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39329</t>
+          <t>37466</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67621</t>
+          <t>68834</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41205</t>
+          <t>42419</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68286</t>
+          <t>69528</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87520</t>
+          <t>86850</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126944</t>
+          <t>126941</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109787</t>
+          <t>109786</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146262</t>
+          <t>145635</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>123357</t>
+          <t>124516</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160715</t>
+          <t>161852</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>242422</t>
+          <t>246046</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>298251</t>
+          <t>297291</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114439</t>
+          <t>115179</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>150760</t>
+          <t>152191</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102403</t>
+          <t>102683</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141032</t>
+          <t>140285</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>226252</t>
+          <t>228341</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>280099</t>
+          <t>280671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,61%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44491</t>
+          <t>45248</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73604</t>
+          <t>75250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35752</t>
+          <t>35651</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63121</t>
+          <t>62307</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87882</t>
+          <t>88102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128166</t>
+          <t>126289</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13681</t>
+          <t>12984</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13234</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60015</t>
+          <t>60585</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91969</t>
+          <t>91820</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22572</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74635</t>
+          <t>72083</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>109939</t>
+          <t>110208</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>142492</t>
+          <t>141367</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>185712</t>
+          <t>183441</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36853</t>
+          <t>37177</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61006</t>
+          <t>61458</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>186452</t>
+          <t>185064</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>234410</t>
+          <t>232332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>154358</t>
+          <t>152770</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>197164</t>
+          <t>195428</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41878</t>
+          <t>41120</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66853</t>
+          <t>66133</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>203795</t>
+          <t>205129</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>252406</t>
+          <t>254506</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85903</t>
+          <t>83698</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>122895</t>
+          <t>122598</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37633</t>
+          <t>37631</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61810</t>
+          <t>63031</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>132623</t>
+          <t>129591</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>177893</t>
+          <t>174863</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>20447</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18354</t>
+          <t>19507</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14955</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34645</t>
+          <t>34255</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>127808</t>
+          <t>126106</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>174777</t>
+          <t>173978</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>87562</t>
+          <t>88721</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>125059</t>
+          <t>126366</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>227745</t>
+          <t>224605</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>286674</t>
+          <t>287177</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>390618</t>
+          <t>390358</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>456079</t>
+          <t>455747</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>272655</t>
+          <t>275078</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>329303</t>
+          <t>331690</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>684326</t>
+          <t>680967</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>767777</t>
+          <t>768867</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>298972</t>
+          <t>299378</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>361380</t>
+          <t>359719</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>224219</t>
+          <t>227406</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>276593</t>
+          <t>278378</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>542101</t>
+          <t>540652</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>621181</t>
+          <t>623131</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>206371</t>
+          <t>204233</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>261455</t>
+          <t>257332</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>133152</t>
+          <t>134309</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>181903</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>353435</t>
+          <t>354838</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>424500</t>
+          <t>423160</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13746</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17778</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9298</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25654</t>
+          <t>26005</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>61403</t>
+          <t>61529</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>95588</t>
+          <t>94839</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>35545</t>
+          <t>36466</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>62071</t>
+          <t>63268</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>104298</t>
+          <t>106376</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>150190</t>
+          <t>145496</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>179861</t>
+          <t>179791</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>226778</t>
+          <t>227097</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>192798</t>
+          <t>193070</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>243386</t>
+          <t>244014</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>386197</t>
+          <t>385253</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>454221</t>
+          <t>454646</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>167504</t>
+          <t>167724</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>213799</t>
+          <t>214725</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>248022</t>
+          <t>246274</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>300963</t>
+          <t>301898</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>429623</t>
+          <t>430625</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>501077</t>
+          <t>501124</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>125386</t>
+          <t>123057</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>166113</t>
+          <t>165154</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>164425</t>
+          <t>166442</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>215556</t>
+          <t>214408</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>303099</t>
+          <t>300573</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>366019</t>
+          <t>365787</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>26172</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>26096</t>
+          <t>26539</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>50652</t>
+          <t>50300</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>79691</t>
+          <t>80109</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>104943</t>
+          <t>106488</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>148696</t>
+          <t>147855</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>166079</t>
+          <t>168067</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>218322</t>
+          <t>214346</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>108724</t>
+          <t>109777</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>143867</t>
+          <t>143676</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>288542</t>
+          <t>287743</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>349254</t>
+          <t>349104</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>408415</t>
+          <t>409528</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>479504</t>
+          <t>479935</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>50073</t>
+          <t>50104</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>78696</t>
+          <t>78685</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>271971</t>
+          <t>274246</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>330829</t>
+          <t>335993</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>330283</t>
+          <t>329690</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>399540</t>
+          <t>400047</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>21419</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>44656</t>
+          <t>42038</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>290161</t>
+          <t>287148</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>353675</t>
+          <t>350321</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>316895</t>
+          <t>318323</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>385944</t>
+          <t>390705</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>24080</t>
+          <t>23598</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>50780</t>
+          <t>47113</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>33491</t>
+          <t>33095</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>61465</t>
+          <t>62200</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>62976</t>
+          <t>62711</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>101038</t>
+          <t>99368</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>437139</t>
+          <t>436121</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>520479</t>
+          <t>520478</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,7 +14968,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>354048</t>
+          <t>351193</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>427399</t>
+          <t>425093</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>809176</t>
+          <t>805210</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>923988</t>
+          <t>924387</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1144301</t>
+          <t>1150301</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1260411</t>
+          <t>1263460</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1110963</t>
+          <t>1112664</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1221508</t>
+          <t>1220084</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2294321</t>
+          <t>2287294</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2448534</t>
+          <t>2444334</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>983738</t>
+          <t>975139</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1090439</t>
+          <t>1089737</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1045880</t>
+          <t>1045341</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1159896</t>
+          <t>1155303</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2066688</t>
+          <t>2067081</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2227465</t>
+          <t>2221856</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>581875</t>
+          <t>578242</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>674744</t>
+          <t>672816</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>772916</t>
+          <t>774506</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>875285</t>
+          <t>875726</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1381541</t>
+          <t>1380784</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1523216</t>
+          <t>1516581</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
